--- a/output/pdf_financials_xlsx/NEXM.xlsx
+++ b/output/pdf_financials_xlsx/NEXM.xlsx
@@ -1486,16 +1486,16 @@
         <v>-9.359605</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>27.30635</v>
+        <v>-27.30635</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>32.376069</v>
+        <v>-32.376069</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>42.420283</v>
+        <v>-42.420283</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>59.086325</v>
+        <v>-59.086325</v>
       </c>
     </row>
     <row r="17">
@@ -1830,16 +1830,16 @@
         <v>-9.359605</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>27.30635</v>
+        <v>-27.30635</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>32.376069</v>
+        <v>-32.376069</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>42.420283</v>
+        <v>-42.420283</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>59.086325</v>
+        <v>-59.086325</v>
       </c>
     </row>
     <row r="21">
@@ -2040,16 +2040,16 @@
         <v>-9.359605</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>27.30635</v>
+        <v>-27.30635</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>32.376069</v>
+        <v>-32.376069</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>42.420283</v>
+        <v>-42.420283</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>59.086325</v>
+        <v>-59.086325</v>
       </c>
     </row>
     <row r="24">
@@ -2258,16 +2258,16 @@
         <v>71.996962</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>109.2254</v>
+        <v>-109.2254</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>129.504276</v>
+        <v>-129.504276</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>8.450256</v>
+        <v>-8.450256</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>20.659554</v>
+        <v>-20.659554</v>
       </c>
     </row>
     <row r="27">
@@ -2328,16 +2328,16 @@
         <v>-9.359605</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>27.30635</v>
+        <v>-27.30635</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>32.376069</v>
+        <v>-32.376069</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>42.420283</v>
+        <v>-42.420283</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>59.086325</v>
+        <v>-59.086325</v>
       </c>
     </row>
     <row r="28">
@@ -2468,16 +2468,16 @@
         <v>-9.359605</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>27.402893</v>
+        <v>-27.209807</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>33.120852</v>
+        <v>-31.631286</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>44.001553</v>
+        <v>-40.839013</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>61.155146</v>
+        <v>-57.017504</v>
       </c>
     </row>
     <row r="30">
@@ -2640,16 +2640,16 @@
         <v>-0</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -3814,7 +3814,7 @@
         <v>0.566634</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.115717</v>
+        <v>0.142</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>0.242</v>
@@ -3823,7 +3823,7 @@
         <v>0.133</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>1.354</v>
+        <v>0.161</v>
       </c>
       <c r="P48" s="3" t="n">
         <v>1.998867</v>
@@ -7014,7 +7014,7 @@
         <v>0</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>0</v>
+        <v>-0.048906</v>
       </c>
       <c r="Q91" s="3" t="n">
         <v>-1.200516</v>
@@ -7062,31 +7062,31 @@
         </is>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.873676</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>3.022767</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>5.199706</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>5.13456</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>2.767</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>5.089</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>7.749</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>4.175</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>1.261891</v>
       </c>
       <c r="Q92" s="3" t="n">
         <v>77.302736</v>
@@ -19178,7 +19178,11 @@
           <t>Reserve</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
           <t>-</t>
@@ -19287,7 +19291,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>-</t>
@@ -19614,7 +19622,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -20815,7 +20823,11 @@
           <t>Reserve 9</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>
@@ -21772,7 +21784,11 @@
           <t>Reserve 10</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
           <t>-</t>
@@ -23617,7 +23633,11 @@
           <t>Reserve 12,13</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
           <t>-</t>
@@ -24380,7 +24400,11 @@
           <t>Share-based payments reserve 12</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
@@ -43294,7 +43318,11 @@
           <t>Trade payables in the prior year for exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D303" t="inlineStr"/>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E303" t="inlineStr">
         <is>
           <t>-</t>
@@ -48322,16 +48350,16 @@
         <v>-9.359605</v>
       </c>
       <c r="T348" s="5" t="n">
-        <v>27.30635</v>
+        <v>-27.30635</v>
       </c>
       <c r="U348" s="5" t="n">
-        <v>32.376069</v>
+        <v>-32.376069</v>
       </c>
       <c r="V348" s="5" t="n">
-        <v>42.420283</v>
+        <v>-42.420283</v>
       </c>
       <c r="W348" s="5" t="n">
-        <v>59.086325</v>
+        <v>-59.086325</v>
       </c>
     </row>
     <row r="349">
@@ -48550,10 +48578,10 @@
         </is>
       </c>
       <c r="V350" s="5" t="n">
-        <v>42.148106</v>
+        <v>-42.148106</v>
       </c>
       <c r="W350" s="5" t="n">
-        <v>60.435852</v>
+        <v>-60.435852</v>
       </c>
     </row>
     <row r="351">
@@ -51974,10 +52002,10 @@
         </is>
       </c>
       <c r="U381" s="5" t="n">
-        <v>32.96454</v>
+        <v>-32.96454</v>
       </c>
       <c r="V381" s="5" t="n">
-        <v>42.148106</v>
+        <v>-42.148106</v>
       </c>
       <c r="W381" t="inlineStr">
         <is>
@@ -56274,10 +56302,10 @@
         </is>
       </c>
       <c r="T420" s="5" t="n">
-        <v>28.48455</v>
+        <v>-28.48455</v>
       </c>
       <c r="U420" s="5" t="n">
-        <v>32.96454</v>
+        <v>-32.96454</v>
       </c>
       <c r="V420" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/NEXM.xlsx
+++ b/output/pdf_financials_xlsx/NEXM.xlsx
@@ -1179,28 +1179,28 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.016062</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.040537</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.081099</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.037</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.028</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.032</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.074</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.026</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>0</v>
@@ -2301,28 +2301,28 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-1.453562</v>
+        <v>-1.469624</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-1.260301</v>
+        <v>-1.300838</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-3.741007</v>
+        <v>-3.822106</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-2.38897</v>
+        <v>-2.42597</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-2.876709</v>
+        <v>-2.904709</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-2.879</v>
+        <v>-2.911</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-3.022</v>
+        <v>-3.096</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-28.859</v>
+        <v>-28.885</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>-9.359605</v>
@@ -2441,28 +2441,28 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.453562</v>
+        <v>-1.469624</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.260301</v>
+        <v>-1.300838</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-3.741007</v>
+        <v>-3.822106</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-2.38897</v>
+        <v>-2.42597</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-2.876709</v>
+        <v>-2.904709</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-2.879</v>
+        <v>-2.911</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-3.022</v>
+        <v>-3.096</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-28.859</v>
+        <v>-28.885</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>-9.359605</v>
@@ -2778,10 +2778,10 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.040661</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.016515</v>
       </c>
       <c r="F34" s="1" t="inlineStr">
         <is>
@@ -2794,16 +2794,16 @@
         </is>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.661245</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.278919</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.326117</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.524923</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>0.63</v>
@@ -2815,10 +2815,10 @@
         <v>0.339</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>1.098</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>1.990203</v>
       </c>
       <c r="Q34" s="3" t="n">
         <v>5.162991</v>
@@ -2922,10 +2922,10 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.040661</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.0625</v>
+        <v>0.079015</v>
       </c>
       <c r="F36" s="1" t="inlineStr">
         <is>
@@ -2938,16 +2938,16 @@
         </is>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.705218</v>
+        <v>1.366463</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>6</v>
+        <v>6.278919</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>6</v>
+        <v>6.326117</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>2.3</v>
+        <v>2.824923</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>3.33</v>
@@ -2959,10 +2959,10 @@
         <v>2.839</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>1.098</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>1.990203</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>5.162991</v>
@@ -3786,10 +3786,10 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.040661</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.016515</v>
+        <v>0</v>
       </c>
       <c r="F48" s="1" t="inlineStr">
         <is>
@@ -3802,19 +3802,19 @@
         </is>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.680015</v>
+        <v>0.01877</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.289617</v>
+        <v>0.010698</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.347516</v>
+        <v>0.021399</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.566634</v>
+        <v>0.041711</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.142</v>
+        <v>0.115717</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>0.242</v>
@@ -3823,10 +3823,10 @@
         <v>0.133</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.161</v>
+        <v>0.256</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>1.998867</v>
+        <v>0.008664</v>
       </c>
       <c r="Q48" s="3" t="n">
         <v>0.470725</v>
@@ -9293,10 +9293,10 @@
         <v>0</v>
       </c>
       <c r="R124" s="3" t="n">
-        <v>0</v>
+        <v>-2.241906</v>
       </c>
       <c r="S124" s="3" t="n">
-        <v>0</v>
+        <v>-1.788454</v>
       </c>
       <c r="T124" s="3" t="n">
         <v>0</v>
@@ -9363,10 +9363,10 @@
         <v>0</v>
       </c>
       <c r="R125" s="3" t="n">
-        <v>0</v>
+        <v>-2.241906</v>
       </c>
       <c r="S125" s="3" t="n">
-        <v>0</v>
+        <v>-1.788454</v>
       </c>
       <c r="T125" s="3" t="n">
         <v>0</v>
@@ -18185,7 +18185,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -19622,7 +19622,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -20173,7 +20173,11 @@
           <t>Reclamation deposit 7</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>-</t>
@@ -22115,7 +22119,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -22864,7 +22868,11 @@
           <t>Reclamation deposit 10</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>
@@ -29956,7 +29964,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr"/>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
           <t>-</t>
@@ -33900,7 +33912,11 @@
           <t>Lease payments 8</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr"/>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E217" t="inlineStr">
         <is>
           <t>-</t>
@@ -36338,7 +36354,11 @@
           <t>Lease payment</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr"/>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E239" t="inlineStr">
         <is>
           <t>-</t>
@@ -41140,7 +41160,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D283" t="inlineStr"/>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E283" t="inlineStr">
         <is>
           <t>-</t>
@@ -43433,7 +43457,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D304" t="inlineStr"/>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E304" t="inlineStr">
         <is>
           <t>-</t>
@@ -47062,7 +47090,11 @@
           <t>General and administrative expenses 2(c),18</t>
         </is>
       </c>
-      <c r="D337" t="inlineStr"/>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E337" t="inlineStr">
         <is>
           <t>-</t>
@@ -54348,7 +54380,11 @@
           <t>General and administration expenses 20</t>
         </is>
       </c>
-      <c r="D403" t="inlineStr"/>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E403" t="inlineStr">
         <is>
           <t>-</t>
@@ -63741,7 +63777,7 @@
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
@@ -67118,7 +67154,7 @@
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E519" t="inlineStr">
@@ -72989,7 +73025,7 @@
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E572" t="inlineStr">

--- a/output/pdf_financials_xlsx/NEXM.xlsx
+++ b/output/pdf_financials_xlsx/NEXM.xlsx
@@ -856,10 +856,10 @@
         <v>0.04039</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0</v>
+        <v>1.020523</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>0</v>
+        <v>0.482396</v>
       </c>
     </row>
     <row r="8">
@@ -1066,10 +1066,10 @@
         <v>30.361043</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0</v>
+        <v>1.020523</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>0</v>
+        <v>0.482396</v>
       </c>
     </row>
     <row r="11">
@@ -1142,10 +1142,10 @@
         <v>-30.361043</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>0</v>
+        <v>-1.020523</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>0</v>
+        <v>-0.482396</v>
       </c>
     </row>
     <row r="12">
@@ -5004,31 +5004,31 @@
         <v>0</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>0.133</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>0.477</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>0</v>
+        <v>0.218456</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>0</v>
+        <v>3.660519</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>0</v>
+        <v>2.383196</v>
       </c>
       <c r="S64" s="3" t="n">
-        <v>0</v>
+        <v>2.493306</v>
       </c>
       <c r="T64" s="3" t="n">
-        <v>0</v>
+        <v>7.147173</v>
       </c>
     </row>
     <row r="65">
@@ -5195,17 +5195,13 @@
         <v>0</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.01</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>0.03918</v>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>0.025249</v>
       </c>
       <c r="H67" s="3" t="n">
         <v>0.063154</v>
@@ -5244,7 +5240,7 @@
         <v>4.47758</v>
       </c>
       <c r="T67" s="3" t="n">
-        <v>0</v>
+        <v>0.751511</v>
       </c>
     </row>
     <row r="68">
@@ -5292,31 +5288,31 @@
         <v>0.249604</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0.181</v>
+        <v>0.314</v>
       </c>
       <c r="M68" s="3" t="n">
-        <v>0.969</v>
+        <v>1.782</v>
       </c>
       <c r="N68" s="3" t="n">
-        <v>0.556</v>
+        <v>1.033</v>
       </c>
       <c r="O68" s="3" t="n">
-        <v>0.519</v>
+        <v>0.829</v>
       </c>
       <c r="P68" s="3" t="n">
-        <v>0.5804859999999999</v>
+        <v>0.798942</v>
       </c>
       <c r="Q68" s="3" t="n">
-        <v>4.025716</v>
+        <v>7.686235</v>
       </c>
       <c r="R68" s="3" t="n">
-        <v>4.280146</v>
+        <v>6.663342</v>
       </c>
       <c r="S68" s="3" t="n">
-        <v>4.47758</v>
+        <v>6.970886</v>
       </c>
       <c r="T68" s="3" t="n">
-        <v>0</v>
+        <v>7.898684</v>
       </c>
     </row>
     <row r="69">
@@ -5454,7 +5450,7 @@
         <v>0</v>
       </c>
       <c r="R70" s="3" t="n">
-        <v>0</v>
+        <v>1.611143</v>
       </c>
       <c r="S70" s="3" t="n">
         <v>0</v>
@@ -5526,7 +5522,7 @@
         <v>0</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>0</v>
+        <v>1.611143</v>
       </c>
       <c r="S71" s="3" t="n">
         <v>0</v>
@@ -5805,22 +5801,22 @@
         <v>0</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>0.089</v>
+        <v>0</v>
       </c>
       <c r="P75" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>8.436655999999999</v>
+        <v>4.776137</v>
       </c>
       <c r="R75" s="3" t="n">
-        <v>1.611143</v>
+        <v>0</v>
       </c>
       <c r="S75" s="3" t="n">
         <v>0</v>
       </c>
       <c r="T75" s="3" t="n">
-        <v>9.957813</v>
+        <v>2.059129</v>
       </c>
     </row>
     <row r="76">
@@ -6207,10 +6203,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R80" s="3" t="n">
+        <v>0.1653185830120117</v>
       </c>
       <c r="S80" s="1" t="inlineStr">
         <is>
@@ -8354,25 +8348,25 @@
         <v>0</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-0.040174</v>
       </c>
       <c r="J111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>0</v>
+        <v>-0.138</v>
       </c>
       <c r="L111" s="3" t="n">
-        <v>0</v>
+        <v>-0.003</v>
       </c>
       <c r="M111" s="3" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="N111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O111" s="3" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="P111" s="3" t="n">
         <v>0</v>
@@ -10016,25 +10010,25 @@
         <v>0</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-0.040174</v>
       </c>
       <c r="J134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K134" s="3" t="n">
-        <v>0</v>
+        <v>-0.138</v>
       </c>
       <c r="L134" s="3" t="n">
-        <v>0</v>
+        <v>-0.003</v>
       </c>
       <c r="M134" s="3" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="N134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O134" s="3" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="P134" s="3" t="n">
         <v>0</v>
@@ -10092,25 +10086,25 @@
         <v>-0.6400090000000001</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>-0.872806</v>
+        <v>-0.91298</v>
       </c>
       <c r="J135" s="3" t="n">
         <v>-1.226744</v>
       </c>
       <c r="K135" s="3" t="n">
-        <v>-2.198</v>
+        <v>-2.336</v>
       </c>
       <c r="L135" s="3" t="n">
-        <v>-2.216</v>
+        <v>-2.219</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>-2.429</v>
+        <v>-2.449</v>
       </c>
       <c r="N135" s="3" t="n">
         <v>-2.664</v>
       </c>
       <c r="O135" s="3" t="n">
-        <v>-2.316</v>
+        <v>-2.321</v>
       </c>
       <c r="P135" s="3" t="n">
         <v>-1.454319</v>
@@ -13860,7 +13854,11 @@
           <t>Lease liabilities 8</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -32255,7 +32253,11 @@
           <t>Deferred tax recovery 17</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr"/>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E202" t="inlineStr">
         <is>
           <t>-</t>
@@ -35133,7 +35135,11 @@
           <t>Deferred tax recovery 19</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr"/>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E228" t="inlineStr">
         <is>
           <t>-</t>
@@ -39973,7 +39979,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr"/>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E272" t="inlineStr">
         <is>
           <t>-</t>
@@ -41384,7 +41394,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr"/>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E285" t="inlineStr">
         <is>
           <t>-</t>
@@ -41927,7 +41941,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D290" t="inlineStr"/>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E290" t="inlineStr">
         <is>
           <t>-</t>
@@ -47312,7 +47330,11 @@
           <t>Director fees</t>
         </is>
       </c>
-      <c r="D339" t="inlineStr"/>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E339" t="inlineStr">
         <is>
           <t>-</t>
